--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_259_R26.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_259_R26.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5496</v>
+        <v>5.0036</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2327</v>
+        <v>3.3506</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3169</v>
+        <v>1.653</v>
       </c>
       <c r="G2" t="n">
         <v>5.949</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1494</v>
+        <v>0.6034</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2794</v>
+        <v>0.3973</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.13</v>
+        <v>0.206</v>
       </c>
       <c r="V2" t="n">
         <v>1.4665</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5046</v>
+        <v>4.5197</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4455</v>
+        <v>2.9756</v>
       </c>
       <c r="F3" t="n">
-        <v>1.059</v>
+        <v>1.5441</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1567</v>
+        <v>2.4554</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.5568</v>
+        <v>3.0309</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7135</v>
+        <v>-0.5756</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3823</v>
+        <v>2.9166</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.4383</v>
+        <v>2.6993</v>
       </c>
       <c r="L3" t="n">
-        <v>2.8205</v>
+        <v>0.2173</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2256</v>
+        <v>-0.4612</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1186</v>
+        <v>0.3317</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.107</v>
+        <v>-0.7929</v>
       </c>
       <c r="P3" t="n">
         <v>1.1598</v>
@@ -688,19 +688,19 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2577</v>
+        <v>0.8736</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9911</v>
+        <v>-0.1138</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2667</v>
+        <v>0.9873</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9304</v>
+        <v>0.031</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>0.1728</v>
       </c>
       <c r="X3" t="n">
         <v>-0.1418</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3161</v>
+        <v>4.2081</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2679</v>
+        <v>3.7355</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0482</v>
+        <v>0.4726</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4554</v>
+        <v>1.6108</v>
       </c>
       <c r="H4" t="n">
-        <v>3.0309</v>
+        <v>0.8345</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5756</v>
+        <v>0.7763</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9166</v>
+        <v>1.4397</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6993</v>
+        <v>0.9747</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2173</v>
+        <v>0.465</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4612</v>
+        <v>0.1711</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3317</v>
+        <v>-0.1401</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7929</v>
+        <v>0.3113</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6699000000000001</v>
+        <v>1.0791</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8215</v>
+        <v>0.6332</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4914</v>
+        <v>0.4459</v>
       </c>
       <c r="V4" t="n">
-        <v>0.031</v>
+        <v>1.7501</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1728</v>
+        <v>2.8223</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,37 +799,37 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.955</v>
+        <v>3.9319</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1001</v>
+        <v>2.9737</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1451</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>2.79</v>
+        <v>1.1567</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5451</v>
+        <v>-1.5568</v>
       </c>
       <c r="I5" t="n">
-        <v>2.245</v>
+        <v>2.7135</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4982</v>
+        <v>1.3823</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1462</v>
+        <v>-1.4383</v>
       </c>
       <c r="L5" t="n">
-        <v>2.352</v>
+        <v>2.8205</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.2256</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6012</v>
+        <v>-0.1186</v>
       </c>
       <c r="O5" t="n">
         <v>-0.107</v>
@@ -844,28 +844,28 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6831</v>
+        <v>0.6851</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0657</v>
+        <v>0.5192</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3826</v>
+        <v>0.1658</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.9304</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.787</v>
+        <v>3.499</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3816</v>
+        <v>4.2744</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4054</v>
+        <v>-0.7754</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6108</v>
+        <v>2.79</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8345</v>
+        <v>0.5451</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7763</v>
+        <v>2.245</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4397</v>
+        <v>3.4982</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9747</v>
+        <v>1.1462</v>
       </c>
       <c r="L6" t="n">
-        <v>0.465</v>
+        <v>2.352</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1711</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1401</v>
+        <v>-0.6012</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3113</v>
+        <v>-0.107</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6581</v>
+        <v>0.2271</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2794</v>
+        <v>0.2401</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3787</v>
+        <v>-0.013</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7501</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>2.8223</v>
+        <v>0.5361</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0817</v>
+        <v>1.509</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3261</v>
+        <v>-0.1457</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7556</v>
+        <v>1.6548</v>
       </c>
       <c r="G7" t="n">
         <v>1.8343</v>
@@ -1000,13 +1000,13 @@
         <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>1.639</v>
+        <v>1.0664</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0578</v>
+        <v>0.586</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5812</v>
+        <v>0.4804</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8698</v>
+        <v>0.9109</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4374</v>
+        <v>1.512</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5675</v>
+        <v>-0.6011</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0565</v>
@@ -1078,13 +1078,13 @@
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.1092</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1889</v>
+        <v>0.2636</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1208</v>
+        <v>-0.1544</v>
       </c>
       <c r="V8" t="n">
         <v>0.3943</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0031</v>
+        <v>-1.4839</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5889</v>
+        <v>-1.8681</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5859</v>
+        <v>0.3842</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5669</v>
@@ -1156,13 +1156,13 @@
         <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6386</v>
+        <v>1.1578</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8496</v>
+        <v>0.5704</v>
       </c>
       <c r="U9" t="n">
-        <v>0.789</v>
+        <v>0.5874</v>
       </c>
       <c r="V9" t="n">
         <v>-2.5387</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.417</v>
+        <v>-2.0728</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8925</v>
+        <v>-1.5819</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5245</v>
+        <v>-0.4909</v>
       </c>
       <c r="G10" t="n">
         <v>-2.066</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.351</v>
+        <v>-0.0068</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3734</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>M. LO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.803</v>
+        <v>-2.198</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4685</v>
+        <v>-2.1619</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3345</v>
+        <v>-0.0361</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1363</v>
+        <v>0.2354</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9255</v>
+        <v>-0.6278</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2108</v>
+        <v>0.8632</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2318</v>
+        <v>0.4287</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2318</v>
+        <v>-0.6988</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.1275</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9045</v>
+        <v>-0.1933</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6938</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2108</v>
+        <v>-0.2643</v>
       </c>
       <c r="P11" t="n">
-        <v>0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R11" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0378</v>
+        <v>0.0305</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4481</v>
+        <v>-0.2711</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4103</v>
+        <v>0.3016</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8608</v>
+        <v>-1.0722</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>-1.0722</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. LO</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8035</v>
+        <v>-2.2894</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3978</v>
+        <v>-0.6861</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4058</v>
+        <v>-1.6033</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2354</v>
+        <v>-1.1363</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6278</v>
+        <v>-0.9255</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8632</v>
+        <v>-0.2108</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4287</v>
+        <v>-0.2318</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6988</v>
+        <v>-0.2318</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1275</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1933</v>
+        <v>-0.9045</v>
       </c>
       <c r="N12" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.6938</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2643</v>
+        <v>-0.2108</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.575</v>
+        <v>0.4758</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.507</v>
+        <v>0.3343</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.06809999999999999</v>
+        <v>0.1415</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0722</v>
+        <v>-1.8608</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2861</v>
+        <v>-3.4138</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.331</v>
+        <v>-1.4922</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9552</v>
+        <v>-1.9216</v>
       </c>
       <c r="G13" t="n">
         <v>-0.951</v>
@@ -1468,13 +1468,13 @@
         <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8246</v>
+        <v>0.6969</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6844</v>
+        <v>0.5232</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1401</v>
+        <v>0.1737</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.7511</v>
+        <v>12.1243</v>
       </c>
       <c r="E14" t="n">
-        <v>10.5126</v>
+        <v>10.8859</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2384</v>
+        <v>1.2385</v>
       </c>
       <c r="G14" t="n">
         <v>11.2549</v>
       </c>
       <c r="H14" t="n">
-        <v>3.0917</v>
+        <v>3.091700000000001</v>
       </c>
       <c r="I14" t="n">
         <v>8.163699999999999</v>
@@ -1525,7 +1525,7 @@
         <v>5.1715</v>
       </c>
       <c r="L14" t="n">
-        <v>9.7689</v>
+        <v>9.768899999999999</v>
       </c>
       <c r="M14" t="n">
         <v>-3.6854</v>
@@ -1546,16 +1546,16 @@
         <v>10.4381</v>
       </c>
       <c r="S14" t="n">
-        <v>6.624700000000001</v>
+        <v>6.9981</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2463</v>
+        <v>3.6196</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3783</v>
+        <v>3.378200000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.6495</v>
+        <v>-2.649500000000001</v>
       </c>
       <c r="W14" t="n">
         <v>6.242800000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.792</v>
+        <v>2.3951</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9517</v>
+        <v>3.0697</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1598</v>
+        <v>-0.6746</v>
       </c>
       <c r="G15" t="n">
         <v>-0.4263</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2003</v>
+        <v>-0.1966</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.55</v>
+        <v>-0.4321</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7503</v>
+        <v>0.2355</v>
       </c>
       <c r="V15" t="n">
         <v>0.9304</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. MIROTIC</t>
+          <t>M. JAMES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3743</v>
+        <v>1.7464</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5419</v>
+        <v>3.4479</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9162</v>
+        <v>-1.7015</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6004</v>
+        <v>-0.7475000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5907</v>
+        <v>-1.3029</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1911</v>
+        <v>0.5553</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4468</v>
+        <v>1.5938</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1595</v>
+        <v>-0.6478</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7127</v>
+        <v>2.2416</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0472</v>
+        <v>-2.3413</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5688</v>
+        <v>-0.6551</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4783</v>
+        <v>-1.6862</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3637</v>
+        <v>-0.97</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8136</v>
+        <v>-0.4321</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1773</v>
+        <v>-0.5379</v>
       </c>
       <c r="V16" t="n">
-        <v>2.5387</v>
+        <v>1.6083</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1444</v>
+        <v>2.2862</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3943</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. JAMES</t>
+          <t>N. MIROTIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0115</v>
+        <v>1.3427</v>
       </c>
       <c r="E17" t="n">
-        <v>3.33</v>
+        <v>-0.306</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3185</v>
+        <v>1.6486</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7475000000000001</v>
+        <v>-0.6004</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3029</v>
+        <v>0.5907</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5553</v>
+        <v>-1.1911</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5938</v>
+        <v>0.4468</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6478</v>
+        <v>1.1595</v>
       </c>
       <c r="L17" t="n">
-        <v>2.2416</v>
+        <v>-0.7127</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.3413</v>
+        <v>-1.0472</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6551</v>
+        <v>-0.5688</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.6862</v>
+        <v>-0.4783</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8556</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7049</v>
+        <v>0.3321</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.55</v>
+        <v>-0.5777</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1549</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>1.6083</v>
+        <v>2.5387</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2862</v>
+        <v>2.1444</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BLOSSOMGAME</t>
+          <t>N. NEDOVIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4021</v>
+        <v>0.6946</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5006</v>
+        <v>0.4086</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0985</v>
+        <v>0.286</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1542</v>
+        <v>1.6291</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0035</v>
+        <v>1.1104</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1506</v>
+        <v>0.5187</v>
       </c>
       <c r="J18" t="n">
-        <v>0.669</v>
+        <v>1.804</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.077</v>
+        <v>0.8605</v>
       </c>
       <c r="L18" t="n">
-        <v>0.746</v>
+        <v>0.9435</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8231</v>
+        <v>-0.175</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9265</v>
+        <v>0.2499</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8966</v>
+        <v>-0.4248</v>
       </c>
       <c r="P18" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>0.93</v>
+        <v>-0.2566</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3135</v>
+        <v>-0.2357</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3835</v>
+        <v>-0.0209</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3943</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2836</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. TARPEY</t>
+          <t>D. MICHINEAU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1147</v>
+        <v>0.2</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6195</v>
+        <v>-0.0344</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7342</v>
+        <v>0.2344</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2264</v>
+        <v>0.2905</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3637</v>
+        <v>0.15</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1373</v>
+        <v>0.1406</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9477</v>
+        <v>0.0403</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9845</v>
+        <v>0.0035</v>
       </c>
       <c r="L19" t="n">
         <v>0.0368</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2787</v>
+        <v>0.2502</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3792</v>
+        <v>0.1465</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1005</v>
+        <v>0.1038</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6427</v>
+        <v>-0.0905</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3462</v>
+        <v>-0.0747</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2965</v>
+        <v>-0.0158</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9304</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. MICHINEAU</t>
+          <t>T. TARPEY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.3679</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0344</v>
+        <v>-2.0913</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1</v>
+        <v>1.7235</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2905</v>
+        <v>-1.2264</v>
       </c>
       <c r="H20" t="n">
-        <v>0.15</v>
+        <v>-1.3637</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1406</v>
+        <v>0.1373</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0403</v>
+        <v>-0.9477</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0035</v>
+        <v>-0.9845</v>
       </c>
       <c r="L20" t="n">
         <v>0.0368</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2502</v>
+        <v>-0.2787</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1465</v>
+        <v>-0.3792</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1038</v>
+        <v>0.1005</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2249</v>
+        <v>0.1601</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0747</v>
+        <v>-0.1256</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1502</v>
+        <v>0.2858</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.9304</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. NEDOVIC</t>
+          <t>J. BLOSSOMGAME</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0517</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0547</v>
+        <v>0.2031</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1065</v>
+        <v>-0.7732</v>
       </c>
       <c r="G21" t="n">
-        <v>1.6291</v>
+        <v>-1.1542</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1104</v>
+        <v>-1.0035</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5187</v>
+        <v>-0.1506</v>
       </c>
       <c r="J21" t="n">
-        <v>1.804</v>
+        <v>0.669</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8605</v>
+        <v>-0.077</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9435</v>
+        <v>0.746</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.175</v>
+        <v>-1.8231</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2499</v>
+        <v>-0.9265</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4248</v>
+        <v>-0.8966</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0029</v>
+        <v>-0.0422</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5895</v>
+        <v>0.016</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4134</v>
+        <v>-0.0582</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.3943</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3499</v>
+        <v>-2.3778</v>
       </c>
       <c r="E22" t="n">
-        <v>0.297</v>
+        <v>0.179</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6469</v>
+        <v>-2.5568</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6172</v>
@@ -2170,13 +2170,13 @@
         <v>2.0876</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9647</v>
+        <v>-0.9926</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2513</v>
+        <v>-0.3692</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7134</v>
+        <v>-0.6234</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5361</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1588</v>
+        <v>-2.8164</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4901</v>
+        <v>-0.3721</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6687</v>
+        <v>-2.4443</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0384</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5843</v>
+        <v>-0.2418</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2908</v>
+        <v>-0.1729</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2934</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5361</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4123</v>
+        <v>-3.5086</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5779</v>
+        <v>-2.224</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8344</v>
+        <v>-1.2846</v>
       </c>
       <c r="G24" t="n">
         <v>-3.5435</v>
@@ -2326,13 +2326,13 @@
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3842</v>
+        <v>-0.4806</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6563</v>
+        <v>-0.3025</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7279</v>
+        <v>-0.1781</v>
       </c>
       <c r="V24" t="n">
         <v>0.2836</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.5385</v>
+        <v>-6.1301</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.1088</v>
+        <v>-3.519</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.4297</v>
+        <v>-2.6111</v>
       </c>
       <c r="G25" t="n">
         <v>-2.8208</v>
@@ -2404,13 +2404,13 @@
         <v>1.6237</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.8954</v>
+        <v>-1.487</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2617</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.6337</v>
+        <v>-0.8151</v>
       </c>
       <c r="V25" t="n">
         <v>-2.2862</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11.751</v>
+        <v>-9.392099999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.238599999999999</v>
+        <v>-1.2385</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.5126</v>
+        <v>-8.153600000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-11.2551</v>
@@ -2452,7 +2452,7 @@
         <v>-3.0914</v>
       </c>
       <c r="I26" t="n">
-        <v>-8.163699999999999</v>
+        <v>-8.1637</v>
       </c>
       <c r="J26" t="n">
         <v>3.6855</v>
@@ -2482,19 +2482,19 @@
         <v>13.9172</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.624599999999999</v>
+        <v>-4.2657</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.3782</v>
+        <v>-3.378399999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.2463</v>
+        <v>-0.8873</v>
       </c>
       <c r="V26" t="n">
-        <v>2.6494</v>
+        <v>2.649399999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>8.892299999999999</v>
+        <v>8.892300000000001</v>
       </c>
       <c r="X26" t="n">
         <v>-6.2429</v>
